--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLVII/LTAIPT_A63F47B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLVII/LTAIPT_A63F47B.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -103,7 +103,7 @@
     <t>Fecha de término del periodo que se informa</t>
   </si>
   <si>
-    <t>Temática de las preguntas frecuentes</t>
+    <t>Temática de las preguntas frecuentes (Redactada con perspectiva de género)</t>
   </si>
   <si>
     <t>Planteamiento de las preguntas frecuentes</t>
@@ -130,28 +130,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>281401EFBA5B3DA5444F87527AF45414</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>11/07/2022</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de abril del 2022 al 30 de junio del 2022, el Colegio de Bachilleres del Estado de Tlaxcala, Con fundamento en el artìculo 4 y 73, fracciòn XVI Bases 2a y 3a de la Carta Magna;  El Colegio de Bachilleres del Estado de Tlaxcala, devido al ACUERDO por el que se establecen las medidas preventivas que se deberán implementar para la mitigación y control de los riesgos para la salud que implica la enfermedad por el virus SARS-CoV2 (COVID-19). En virtud de lo anterior el Subsistema no se generó listado de de acuerdo a este tema.</t>
+    <t>0F6B0B007FB2C61A27B99758FDCFA982</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>Área de Transparencia</t>
+  </si>
+  <si>
+    <t>10/07/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de abril del 2023 al 30 de junio del 2023, el Colegio de Bachilleres del Estado de Tlaxcala no generó política en referencia a este tema.</t>
   </si>
 </sst>
 </file>
@@ -547,11 +547,11 @@
   <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="66.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="53.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="40.7109375" bestFit="1" customWidth="1"/>
@@ -559,7 +559,7 @@
     <col min="10" max="10" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="255" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="140.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
